--- a/docs/app01.file/人工智能学院通讯录(1).xlsx
+++ b/docs/app01.file/人工智能学院通讯录(1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="2" r:id="rId1"/>
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="108">
-  <si>
-    <t>人工智能学院通讯录</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+  <si>
+    <t>人工智能学院教师名单</t>
   </si>
   <si>
     <t>岗位</t>
@@ -38,48 +38,10 @@
     <t>姓名</t>
   </si>
   <si>
-    <t>办公电话</t>
-  </si>
-  <si>
-    <t>内线</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>手</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>机</t>
-    </r>
-  </si>
-  <si>
-    <t>短 号</t>
-  </si>
-  <si>
-    <t>办公地点</t>
+    <t>安排场次</t>
+  </si>
+  <si>
+    <t>分组</t>
   </si>
   <si>
     <t>院长</t>
@@ -88,82 +50,21 @@
     <t>谭 旭</t>
   </si>
   <si>
-    <t>13760330247 </t>
-  </si>
-  <si>
-    <t>科技楼1511</t>
-  </si>
-  <si>
-    <t>理论上不排监考</t>
-  </si>
-  <si>
     <t>副书记</t>
   </si>
   <si>
     <t>回俊青</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="仿宋"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve"> 89226091 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>科技楼1509</t>
-  </si>
-  <si>
     <t>副院长</t>
   </si>
   <si>
     <t>但唐仁</t>
   </si>
   <si>
-    <t>13724330792</t>
-  </si>
-  <si>
-    <t>科技楼1510</t>
-  </si>
-  <si>
     <t>程东升</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="仿宋"/>
-        <charset val="0"/>
-      </rPr>
-      <t>89229663</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF111111"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>科技楼1508</t>
-  </si>
-  <si>
     <t>吕长伟</t>
   </si>
   <si>
@@ -173,31 +74,19 @@
     <t>潘清华</t>
   </si>
   <si>
-    <t>科技楼1504</t>
-  </si>
-  <si>
-    <t>二级机构（少排一场）</t>
-  </si>
-  <si>
     <t>肖睿毅</t>
   </si>
   <si>
     <t>程一凡</t>
   </si>
   <si>
-    <t>不排监考</t>
-  </si>
-  <si>
     <t>教务办公室</t>
   </si>
   <si>
     <t>刘婷婷</t>
   </si>
   <si>
-    <t>13632642179</t>
-  </si>
-  <si>
-    <t>科技楼1512</t>
+    <t>A</t>
   </si>
   <si>
     <t>钟紫绢</t>
@@ -212,73 +101,40 @@
     <t>张 翔</t>
   </si>
   <si>
-    <t>89226350</t>
-  </si>
-  <si>
-    <t>13425134913</t>
-  </si>
-  <si>
-    <t>科技楼302</t>
-  </si>
-  <si>
     <t>武艳艳</t>
   </si>
   <si>
-    <t>13823169687</t>
-  </si>
-  <si>
     <t>王晓寒</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>聂子凡</t>
   </si>
   <si>
-    <t>19200209727 </t>
-  </si>
-  <si>
     <t>梁 言</t>
   </si>
   <si>
-    <t>18035970099 </t>
-  </si>
-  <si>
     <t>实训室</t>
   </si>
   <si>
     <t>段 虎</t>
   </si>
   <si>
-    <t>89226347</t>
-  </si>
-  <si>
-    <t>13421330827</t>
-  </si>
-  <si>
-    <t>知行楼7-305</t>
-  </si>
-  <si>
     <t>黄晓东</t>
   </si>
   <si>
-    <t>13510241776</t>
+    <t>c</t>
   </si>
   <si>
     <t>秦 天</t>
   </si>
   <si>
-    <t>15013860767</t>
-  </si>
-  <si>
     <t>云计算技术应用专业教研室</t>
   </si>
   <si>
     <t>孔令晶</t>
-  </si>
-  <si>
-    <t>18320905936</t>
-  </si>
-  <si>
-    <t>科技楼1502</t>
   </si>
   <si>
     <t>周 莹</t>
@@ -313,13 +169,7 @@
     </r>
   </si>
   <si>
-    <t>13926553718</t>
-  </si>
-  <si>
     <t>黄瑾瑜</t>
-  </si>
-  <si>
-    <t>13760247663</t>
   </si>
   <si>
     <r>
@@ -351,9 +201,6 @@
     </r>
   </si>
   <si>
-    <t>15220179169</t>
-  </si>
-  <si>
     <t>郭明雪</t>
   </si>
   <si>
@@ -366,39 +213,13 @@
     <t>曹 维</t>
   </si>
   <si>
-    <t>科技楼1505</t>
-  </si>
-  <si>
     <t>盛建强</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="仿宋"/>
-        <charset val="134"/>
-      </rPr>
-      <t>89226179</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF111111"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
     <t>陈 康</t>
   </si>
   <si>
     <t>刘 振</t>
-  </si>
-  <si>
-    <t>18719130906 </t>
   </si>
   <si>
     <t>冯昊港</t>
@@ -433,21 +254,12 @@
     </r>
   </si>
   <si>
-    <t>18098943946</t>
-  </si>
-  <si>
     <t>大数据技术专业教研室</t>
   </si>
   <si>
     <t>蒋丰泽</t>
   </si>
   <si>
-    <t>18681500965 </t>
-  </si>
-  <si>
-    <t>科技楼1506</t>
-  </si>
-  <si>
     <t>刘含波</t>
   </si>
   <si>
@@ -460,30 +272,18 @@
     <t>黄国伟</t>
   </si>
   <si>
-    <t>15817300590</t>
-  </si>
-  <si>
     <t>高维春</t>
   </si>
   <si>
-    <t>18028750902</t>
-  </si>
-  <si>
     <t>白雪峰</t>
   </si>
   <si>
-    <t>18819051560</t>
-  </si>
-  <si>
     <t>耿 煜</t>
   </si>
   <si>
     <t>张俊鹏</t>
   </si>
   <si>
-    <t>知行楼3-409</t>
-  </si>
-  <si>
     <t>谢天明</t>
   </si>
   <si>
@@ -494,9 +294,6 @@
   </si>
   <si>
     <t>诸振家</t>
-  </si>
-  <si>
-    <t>科技楼1501</t>
   </si>
   <si>
     <t>洪莹莹</t>
@@ -521,7 +318,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -537,12 +334,6 @@
     <font>
       <sz val="28"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="28"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -564,18 +355,6 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="仿宋"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="仿宋"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -721,18 +500,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF111111"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -968,59 +735,7 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -1045,10 +760,56 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -1059,13 +820,13 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="thin">
         <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1186,137 +947,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1326,81 +1087,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1935,978 +1671,458 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultColWidth="11.3333333333333" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:D49"/>
+  <sheetFormatPr defaultColWidth="11.3307692307692" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="20.8888888888889" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.3333333333333" style="1"/>
-    <col min="3" max="3" width="13.4444444444444" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="7" width="16.2222222222222" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="11.3333333333333" style="1"/>
+    <col min="1" max="1" width="20.8923076923077" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3307692307692" style="1"/>
+    <col min="3" max="3" width="23.3307692307692" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.3307692307692" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38.25" spans="1:8">
+    <row r="1" ht="40" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:8">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1" spans="1:4">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+    </row>
+    <row r="3" ht="17.5" spans="1:4">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" ht="17.5" spans="1:4">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" ht="18.75" spans="1:8">
-      <c r="A3" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" ht="17.5" spans="1:4">
+      <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8">
-        <v>89226195</v>
-      </c>
-      <c r="D3" s="8">
-        <v>6195</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="8">
-        <v>690247</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" ht="17.5" spans="1:4">
+      <c r="A6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" ht="17.5" spans="1:4">
+      <c r="A7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" ht="18.75" spans="1:8">
-      <c r="A4" s="6" t="s">
+      <c r="C7" s="5"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" ht="17.5" spans="1:4">
+      <c r="A8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C8" s="5"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" ht="17.5" spans="1:4">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="8">
-        <v>6091</v>
-      </c>
-      <c r="E4" s="8">
-        <v>13544234285</v>
-      </c>
-      <c r="F4" s="8">
-        <v>664285</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="C9" s="5"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" ht="17.5" spans="1:4">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="18.75" spans="1:8">
-      <c r="A5" s="6" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" ht="17.5" spans="1:4">
+      <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="8">
-        <v>89226182</v>
-      </c>
-      <c r="D5" s="8">
-        <v>6182</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="C11" s="5"/>
+      <c r="D11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="8">
-        <v>610792</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="18.75" spans="1:8">
-      <c r="A6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="8">
-        <v>9663</v>
-      </c>
-      <c r="E6" s="8">
-        <v>13530257002</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" spans="1:8">
-      <c r="A7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="8">
-        <v>89226909</v>
-      </c>
-      <c r="D7" s="8">
-        <v>6909</v>
-      </c>
-      <c r="E7" s="8">
-        <v>18565767918</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" spans="1:8">
-      <c r="A8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="8">
-        <v>89226342</v>
-      </c>
-      <c r="D8" s="8">
-        <v>6342</v>
-      </c>
-      <c r="E8" s="8">
-        <v>15019414985</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" spans="1:8">
-      <c r="A9" s="11"/>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="8">
-        <v>89226342</v>
-      </c>
-      <c r="D9" s="8">
-        <v>6342</v>
-      </c>
-      <c r="E9" s="8">
-        <v>13823229399</v>
-      </c>
-      <c r="F9" s="8">
-        <v>679399</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" spans="1:8">
-      <c r="A10" s="11"/>
-      <c r="B10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="8">
-        <v>89226342</v>
-      </c>
-      <c r="D10" s="8">
-        <v>6342</v>
-      </c>
-      <c r="E10" s="8">
-        <v>15220202303</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" spans="1:8">
-      <c r="A11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="8">
-        <v>89226354</v>
-      </c>
-      <c r="D11" s="8">
-        <v>6354</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="8">
-        <v>62179</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" ht="18.75" spans="1:8">
+    </row>
+    <row r="12" ht="17.5" spans="1:4">
       <c r="A12" s="11"/>
       <c r="B12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" ht="17.5" spans="1:4">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" ht="17.5" spans="1:4">
+      <c r="A14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" ht="17.5" spans="1:4">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" ht="17.5" spans="1:4">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" ht="17.5" spans="1:4">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" ht="17.5" spans="1:4">
+      <c r="A18" s="13"/>
+      <c r="B18" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" ht="17.5" spans="1:4">
+      <c r="A19" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" ht="17.5" spans="1:4">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" ht="17.5" spans="1:4">
+      <c r="A21" s="13"/>
+      <c r="B21" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" ht="17.5" spans="1:4">
+      <c r="A22" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" ht="17.5" spans="1:4">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="8">
-        <v>89226349</v>
-      </c>
-      <c r="D12" s="8">
-        <v>6349</v>
-      </c>
-      <c r="E12" s="8">
-        <v>15976886700</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" spans="1:8">
-      <c r="A13" s="11"/>
-      <c r="B13" s="6" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" ht="17.5" spans="1:4">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="8">
-        <v>89226349</v>
-      </c>
-      <c r="D13" s="8">
-        <v>6349</v>
-      </c>
-      <c r="E13" s="8">
-        <v>18666663321</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" ht="18.75" spans="1:8">
-      <c r="A14" s="9" t="s">
+      <c r="C24" s="5"/>
+      <c r="D24" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" ht="17.5" spans="1:4">
+      <c r="A25" s="11"/>
+      <c r="B25" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C25" s="5"/>
+      <c r="D25" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" ht="17.5" spans="1:4">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C26" s="5"/>
+      <c r="D26" s="6"/>
+    </row>
+    <row r="27" ht="17.5" spans="1:4">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="8">
-        <v>6350</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="C27" s="5"/>
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" ht="17.5" spans="1:4">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="8">
-        <v>664913</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="C28" s="5"/>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" ht="17.5" spans="1:4">
+      <c r="A29" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" spans="1:8">
-      <c r="A15" s="11"/>
-      <c r="B15" s="6" t="s">
+      <c r="B29" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="8">
-        <v>6350</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="C29" s="5"/>
+      <c r="D29" s="6"/>
+    </row>
+    <row r="30" ht="17.5" spans="1:4">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="8">
-        <v>669687</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" ht="18.75" spans="1:8">
-      <c r="A16" s="11"/>
-      <c r="B16" s="6" t="s">
+      <c r="C30" s="5"/>
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" ht="17.5" spans="1:4">
+      <c r="A31" s="11"/>
+      <c r="B31" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="8">
-        <v>6350</v>
-      </c>
-      <c r="E16" s="8">
-        <v>15973126330</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" ht="18.75" spans="1:8">
-      <c r="A17" s="11"/>
-      <c r="B17" s="6" t="s">
+      <c r="C31" s="5"/>
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" ht="17.5" spans="1:4">
+      <c r="A32" s="11"/>
+      <c r="B32" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="8">
-        <v>6350</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="C32" s="5"/>
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" ht="17.5" spans="1:4">
+      <c r="A33" s="11"/>
+      <c r="B33" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" ht="18.75" spans="1:8">
-      <c r="A18" s="12"/>
-      <c r="B18" s="6" t="s">
+      <c r="C33" s="5"/>
+      <c r="D33" s="6"/>
+    </row>
+    <row r="34" ht="17.5" spans="1:4">
+      <c r="A34" s="11"/>
+      <c r="B34" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="8">
-        <v>6350</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="C34" s="5"/>
+      <c r="D34" s="6"/>
+    </row>
+    <row r="35" ht="17.5" spans="1:4">
+      <c r="A35" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" ht="18.75" spans="1:8">
-      <c r="A19" s="9" t="s">
+      <c r="B35" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="C35" s="5"/>
+      <c r="D35" s="6"/>
+    </row>
+    <row r="36" ht="17.5" spans="1:4">
+      <c r="A36" s="15"/>
+      <c r="B36" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C36" s="5"/>
+      <c r="D36" s="6"/>
+    </row>
+    <row r="37" ht="17.5" spans="1:4">
+      <c r="A37" s="15"/>
+      <c r="B37" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="14">
-        <v>6347</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="C37" s="5"/>
+      <c r="D37" s="6"/>
+    </row>
+    <row r="38" ht="17.5" spans="1:4">
+      <c r="A38" s="15"/>
+      <c r="B38" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="8">
-        <v>66827</v>
-      </c>
-      <c r="G19" s="8" t="s">
+      <c r="C38" s="5"/>
+      <c r="D38" s="6"/>
+    </row>
+    <row r="39" ht="17.5" spans="1:4">
+      <c r="A39" s="15"/>
+      <c r="B39" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" ht="18.75" spans="1:8">
-      <c r="A20" s="11"/>
-      <c r="B20" s="6" t="s">
+      <c r="C39" s="5"/>
+      <c r="D39" s="6"/>
+    </row>
+    <row r="40" ht="17.5" spans="1:4">
+      <c r="A40" s="15"/>
+      <c r="B40" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="14">
-        <v>6347</v>
-      </c>
-      <c r="E20" s="8" t="s">
+      <c r="C40" s="5"/>
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41" ht="17.5" spans="1:4">
+      <c r="A41" s="15"/>
+      <c r="B41" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="8">
-        <v>641776</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" ht="18.75" spans="1:8">
-      <c r="A21" s="12"/>
-      <c r="B21" s="6" t="s">
+      <c r="C41" s="5"/>
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" ht="17.5" spans="1:4">
+      <c r="A42" s="15"/>
+      <c r="B42" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="14">
-        <v>6347</v>
-      </c>
-      <c r="E21" s="8" t="s">
+      <c r="C42" s="5"/>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" ht="17.5" spans="1:4">
+      <c r="A43" s="15"/>
+      <c r="B43" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F21" s="8">
-        <v>660767</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" ht="18.75" spans="1:8">
-      <c r="A22" s="9" t="s">
+      <c r="C43" s="5"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" ht="17.5" spans="1:4">
+      <c r="A44" s="15"/>
+      <c r="B44" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="C44" s="5"/>
+      <c r="D44" s="6"/>
+    </row>
+    <row r="45" ht="17.5" spans="1:4">
+      <c r="A45" s="15"/>
+      <c r="B45" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="8" t="s">
+      <c r="C45" s="5"/>
+      <c r="D45" s="6"/>
+    </row>
+    <row r="46" ht="17.5" spans="1:4">
+      <c r="A46" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="8">
-        <v>69331</v>
-      </c>
-      <c r="G22" s="8" t="s">
+      <c r="B46" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="18.75" spans="1:8">
-      <c r="A23" s="11"/>
-      <c r="B23" s="6" t="s">
+      <c r="C46" s="5"/>
+      <c r="D46" s="6"/>
+    </row>
+    <row r="47" ht="17.5" spans="1:4">
+      <c r="A47" s="15"/>
+      <c r="B47" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="8">
-        <v>13824350104</v>
-      </c>
-      <c r="F23" s="8">
-        <v>610104</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" ht="18.75" spans="1:8">
-      <c r="A24" s="11"/>
-      <c r="B24" s="6" t="s">
+      <c r="C47" s="5"/>
+      <c r="D47" s="6"/>
+    </row>
+    <row r="48" ht="17.5" spans="1:4">
+      <c r="A48" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="8" t="s">
+      <c r="B48" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F24" s="8">
-        <v>613718</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" ht="18.75" spans="1:8">
-      <c r="A25" s="11"/>
-      <c r="B25" s="6" t="s">
+      <c r="C48" s="5"/>
+      <c r="D48" s="6"/>
+    </row>
+    <row r="49" ht="22" customHeight="1" spans="1:4">
+      <c r="A49" s="15"/>
+      <c r="B49" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F25" s="8">
-        <v>6618</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" ht="18.75" spans="1:8">
-      <c r="A26" s="11"/>
-      <c r="B26" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" s="8">
-        <v>669169</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" ht="18.75" spans="1:8">
-      <c r="A27" s="11"/>
-      <c r="B27" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6">
-        <v>18844548389</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" ht="18.75" spans="1:8">
-      <c r="A28" s="11"/>
-      <c r="B28" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6">
-        <v>15919865031</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" ht="18.75" spans="1:8">
-      <c r="A29" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="17">
-        <v>89226175</v>
-      </c>
-      <c r="D29" s="17">
-        <v>6175</v>
-      </c>
-      <c r="E29" s="17">
-        <v>15623122394</v>
-      </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" ht="18.75" spans="1:8">
-      <c r="A30" s="11"/>
-      <c r="B30" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="17">
-        <v>6179</v>
-      </c>
-      <c r="E30" s="17">
-        <v>18822816315</v>
-      </c>
-      <c r="F30" s="17">
-        <v>66315</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" ht="18.75" spans="1:8">
-      <c r="A31" s="11"/>
-      <c r="B31" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17">
-        <v>18500354860</v>
-      </c>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" ht="18.75" spans="1:8">
-      <c r="A32" s="11"/>
-      <c r="B32" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" ht="18.75" spans="1:8">
-      <c r="A33" s="11"/>
-      <c r="B33" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="17">
-        <v>13798210432</v>
-      </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" ht="18.75" spans="1:8">
-      <c r="A34" s="11"/>
-      <c r="B34" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" ht="18.75" spans="1:8">
-      <c r="A35" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="17">
-        <v>89226175</v>
-      </c>
-      <c r="D35" s="17">
-        <v>6175</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" ht="18.75" spans="1:8">
-      <c r="A36" s="19"/>
-      <c r="B36" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" s="17">
-        <v>89226175</v>
-      </c>
-      <c r="D36" s="17">
-        <v>6175</v>
-      </c>
-      <c r="E36" s="17">
-        <v>13751019870</v>
-      </c>
-      <c r="F36" s="17">
-        <v>68870</v>
-      </c>
-      <c r="G36" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" ht="18.75" spans="1:8">
-      <c r="A37" s="19"/>
-      <c r="B37" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="17">
-        <v>89226175</v>
-      </c>
-      <c r="D37" s="17">
-        <v>6175</v>
-      </c>
-      <c r="E37" s="17">
-        <v>13554958843</v>
-      </c>
-      <c r="F37" s="17">
-        <v>68843</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" ht="18.75" spans="1:8">
-      <c r="A38" s="19"/>
-      <c r="B38" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="17">
-        <v>17503079106</v>
-      </c>
-      <c r="F38" s="17"/>
-      <c r="G38" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" ht="18.75" spans="1:8">
-      <c r="A39" s="19"/>
-      <c r="B39" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="F39" s="8">
-        <v>66590</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" ht="18.75" spans="1:8">
-      <c r="A40" s="19"/>
-      <c r="B40" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F40" s="8">
-        <v>62059</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" ht="18.75" spans="1:8">
-      <c r="A41" s="19"/>
-      <c r="B41" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="F41" s="8">
-        <v>661560</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" ht="18.75" spans="1:8">
-      <c r="A42" s="19"/>
-      <c r="B42" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" s="6">
-        <v>89226174</v>
-      </c>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6">
-        <v>13714887156</v>
-      </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" ht="18.75" spans="1:8">
-      <c r="A43" s="19"/>
-      <c r="B43" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6">
-        <v>13302313228</v>
-      </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" ht="18.75" spans="1:8">
-      <c r="A44" s="19"/>
-      <c r="B44" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6">
-        <v>17855105454</v>
-      </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" ht="18.75" spans="1:8">
-      <c r="A45" s="19"/>
-      <c r="B45" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6">
-        <v>13823563139</v>
-      </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" ht="18.75" spans="1:8">
-      <c r="A46" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="C46" s="6">
-        <v>89226923</v>
-      </c>
-      <c r="D46" s="17">
-        <v>6923</v>
-      </c>
-      <c r="E46" s="17">
-        <v>13510593509</v>
-      </c>
-      <c r="F46" s="17">
-        <v>662281</v>
-      </c>
-      <c r="G46" s="17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" ht="18.75" spans="1:8">
-      <c r="A47" s="19"/>
-      <c r="B47" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C47" s="9">
-        <v>89226923</v>
-      </c>
-      <c r="D47" s="23">
-        <v>6923</v>
-      </c>
-      <c r="E47" s="23">
-        <v>17850509859</v>
-      </c>
-      <c r="F47" s="24"/>
-      <c r="G47" s="25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" ht="18.75" spans="1:8">
-      <c r="A48" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="23">
-        <v>18574405000</v>
-      </c>
-      <c r="F48" s="26"/>
-      <c r="G48" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1" spans="1:7">
-      <c r="A49" s="19"/>
-      <c r="B49" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="27">
-        <v>15889534982</v>
-      </c>
-      <c r="F49" s="26"/>
-      <c r="G49" s="6" t="s">
-        <v>98</v>
-      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="6"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
   <mergeCells count="10">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A18"/>
